--- a/MODELO_Memorial_Planilha_Declaração_R00.xlsx
+++ b/MODELO_Memorial_Planilha_Declaração_R00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\ProTool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF573A6-6B54-4C3F-90D6-BEB12BAA34BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D79BE1E-285F-4D27-8441-6C91A4FBA7AB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="5" r:id="rId1"/>
@@ -28,15 +28,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -895,7 +886,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1036,10 +1027,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1056,10 +1043,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1114,10 +1097,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1128,14 +1107,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1146,74 +1161,54 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1580,7 +1575,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="54" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1600,7 +1595,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="109" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1620,7 +1615,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="109" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1630,25 +1625,25 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="54" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="64" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="55" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="79" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1656,17 +1651,17 @@
       <c r="A16" s="42"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="64" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="110" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="64" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1681,7 +1676,7 @@
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="110" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1696,7 +1691,7 @@
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="56" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1706,7 +1701,7 @@
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="56" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1716,7 +1711,7 @@
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="56" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1726,7 +1721,7 @@
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="56" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1736,12 +1731,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="56" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="58" t="str">
+      <c r="A34" s="57" t="str">
         <f>"" &amp; Dados!A25 &amp; ", lote " &amp; Dados!A27 &amp; ", quadra " &amp; Dados!A29 &amp; ", LOTEAMENTO "&amp; Dados!A31 &amp;", SORRISO/MT."</f>
         <v>{{confrontacao_frente}}, lote {{lote}}, quadra {{quadra}}, LOTEAMENTO {{loteamento}}, SORRISO/MT.</v>
       </c>
@@ -1754,7 +1749,7 @@
       <c r="B35" s="47"/>
     </row>
     <row r="36" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="111" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1767,7 +1762,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="111" t="s">
         <v>145</v>
       </c>
     </row>
@@ -1777,7 +1772,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="112" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1787,7 +1782,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="60" t="s">
+      <c r="A42" s="112" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1797,7 +1792,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="60" t="s">
+      <c r="A44" s="58" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1807,7 +1802,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="63" t="s">
+      <c r="A46" s="61" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1827,7 +1822,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="60" t="s">
+      <c r="A50" s="58" t="s">
         <v>142</v>
       </c>
     </row>
@@ -1847,18 +1842,18 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="61" t="s">
+      <c r="A54" s="59" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="65" t="str">
+      <c r="A55" s="63" t="str">
         <f>IF(A54="LEANDRO DE SOUZA PEREIRA", "1214579051", IF(A54="PAULO MIGUEL GOULART DAL ZOT", "1222999722", "NOME NÃO ENCONTRADO"))</f>
         <v>1214579051</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="61" t="s">
+      <c r="A56" s="59" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1868,11 +1863,11 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="62" t="str">
+      <c r="A59" s="60" t="str">
         <f ca="1">"Sorriso/MT, " &amp; TEXT(TODAY(),"dd ""de"" mmmm ""de"" aaaa")</f>
         <v>Sorriso/MT, 18 de maio de 2026</v>
       </c>
-      <c r="D59" s="77"/>
+      <c r="D59" s="75"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -1880,7 +1875,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="61" t="s">
+      <c r="A62" s="59" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1939,18 +1934,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -2014,19 +2009,19 @@
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="85"/>
+      <c r="E6" s="82"/>
       <c r="F6" s="6"/>
       <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="84"/>
-      <c r="J6" s="85"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
@@ -2038,39 +2033,39 @@
         <f>Dados!A27</f>
         <v>{{lote}}</v>
       </c>
-      <c r="D7" s="95" t="str">
+      <c r="D7" s="84" t="str">
         <f>Dados!A29</f>
         <v>{{quadra}}</v>
       </c>
-      <c r="E7" s="90"/>
+      <c r="E7" s="86"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="108" t="str">
+      <c r="H7" s="90" t="str">
         <f>Dados!A31</f>
         <v>{{loteamento}}</v>
       </c>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="92"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="85"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="82"/>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
         <v>4</v>
       </c>
-      <c r="H9" s="83" t="s">
+      <c r="H9" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="84"/>
-      <c r="J9" s="85"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="82"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
@@ -2083,12 +2078,12 @@
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="107" t="str">
+      <c r="H10" s="87" t="str">
         <f>Dados!A22</f>
         <v>{{area}}</v>
       </c>
-      <c r="I10" s="92"/>
-      <c r="J10" s="93"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
@@ -2100,12 +2095,12 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="85"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="82"/>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
         <v>6</v>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
       <c r="F13" s="6"/>
       <c r="G13" s="4"/>
       <c r="H13" s="11"/>
@@ -2130,21 +2125,21 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="100" t="str">
+      <c r="B14" s="93" t="str">
         <f>IF(AND(Dados!A16&lt;&gt;"", Dados!B16&lt;&gt;""), Dados!A16,"")</f>
         <v/>
       </c>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="79" t="str">
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="76" t="str">
         <f>IF(Dados!A16&lt;&gt;"",Dados!A16,"")</f>
         <v/>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="90"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="86"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
@@ -2156,35 +2151,35 @@
       <c r="A16" s="4">
         <v>7</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="85"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="82"/>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>8</v>
       </c>
-      <c r="H16" s="83" t="s">
+      <c r="H16" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="84"/>
-      <c r="J16" s="85"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="90"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="86"/>
       <c r="F17" s="8"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="107">
+      <c r="H17" s="87">
         <v>0</v>
       </c>
-      <c r="I17" s="92"/>
-      <c r="J17" s="93"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -2197,12 +2192,12 @@
       <c r="D19" s="5">
         <v>10</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="85"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="82"/>
       <c r="I19" s="12">
         <v>11</v>
       </c>
@@ -2212,19 +2207,19 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="89" t="str">
+      <c r="B20" s="107" t="str">
         <f>E10</f>
         <v>{{area_construida_total}}</v>
       </c>
-      <c r="C20" s="90"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="91">
+      <c r="E20" s="108">
         <f>B17+H17</f>
         <v>0</v>
       </c>
-      <c r="F20" s="92"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="93"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="89"/>
       <c r="I20" s="15"/>
       <c r="J20" s="46" t="str">
         <f>B20</f>
@@ -2235,51 +2230,51 @@
       <c r="A22" s="4">
         <v>12</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="85"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="82"/>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>13</v>
       </c>
-      <c r="H22" s="83" t="s">
+      <c r="H22" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="84"/>
-      <c r="J22" s="85"/>
-      <c r="L22" s="80"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="82"/>
+      <c r="L22" s="77"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="89" t="str">
+      <c r="B23" s="107" t="str">
         <f>B20</f>
         <v>{{area_construida_total}}</v>
       </c>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="90"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="86"/>
       <c r="F23" s="8"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="95" t="str">
+      <c r="H23" s="84" t="str">
         <f>Dados!A44</f>
         <v>{{numero_vagas}}</v>
       </c>
-      <c r="I23" s="94"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="86"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>14</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="85"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="82"/>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
         <v>15</v>
@@ -2296,13 +2291,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="86" t="e">
+      <c r="B26" s="95" t="e">
         <f>1-((B23)/H10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="88"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="97"/>
       <c r="F26" s="8"/>
       <c r="G26" s="7"/>
       <c r="H26" s="16" t="str">
@@ -2319,54 +2314,54 @@
       <c r="A28" s="4">
         <v>17</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="85"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="82"/>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>18</v>
       </c>
-      <c r="H28" s="83" t="s">
+      <c r="H28" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="I28" s="84"/>
-      <c r="J28" s="85"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="82"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="86" t="e">
+      <c r="B29" s="95" t="e">
         <f>B23/H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="88"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="97"/>
       <c r="F29" s="8"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="96" t="e">
+      <c r="H29" s="98" t="e">
         <f>B20/H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I29" s="97"/>
-      <c r="J29" s="98"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="100"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>19</v>
       </c>
-      <c r="B31" s="100" t="s">
+      <c r="B31" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="67" t="str">
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="65" t="str">
         <f>IF(Dados!A14=J31, "X", "")</f>
         <v>X</v>
       </c>
@@ -2375,18 +2370,18 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="101"/>
-      <c r="B32" s="102" t="str">
+      <c r="A32" s="102"/>
+      <c r="B32" s="103" t="str">
         <f>Dados!A12</f>
         <v>RESIDENCIAL E COMERCIAL</v>
       </c>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="102"/>
-      <c r="I32" s="67" t="str">
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="65" t="str">
         <f>IF(Dados!A14=J32, "X", "")</f>
         <v/>
       </c>
@@ -2395,15 +2390,15 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="101"/>
-      <c r="B33" s="102"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="102"/>
-      <c r="H33" s="102"/>
-      <c r="I33" s="67" t="str">
+      <c r="A33" s="102"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="65" t="str">
         <f>IF(Dados!A14=J33, "X", "")</f>
         <v/>
       </c>
@@ -2418,70 +2413,70 @@
       <c r="H35" t="s">
         <v>27</v>
       </c>
-      <c r="J35" s="80"/>
+      <c r="J35" s="77"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O37" s="22"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="103" t="str">
+      <c r="B39" s="104" t="str">
         <f>C3</f>
         <v>{{proprietario_1}}</v>
       </c>
-      <c r="C39" s="103"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="H39" s="103" t="str">
+      <c r="C39" s="104"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="H39" s="104" t="str">
         <f>Dados!A54</f>
         <v>LEANDRO DE SOUZA PEREIRA</v>
       </c>
-      <c r="I39" s="103"/>
-      <c r="J39" s="103"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="104" t="str">
+      <c r="B40" s="105" t="str">
         <f>B4</f>
         <v>{{num_doc_1}}</v>
       </c>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="H40" s="105" t="str">
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="H40" s="106" t="str">
         <f>Dados!A55</f>
         <v>1214579051</v>
       </c>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
+      <c r="I40" s="106"/>
+      <c r="J40" s="106"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="99"/>
-      <c r="C42" s="99"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="99"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="101"/>
+      <c r="D42" s="101"/>
+      <c r="E42" s="101"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="99" t="str">
+      <c r="B43" s="101" t="str">
         <f>IF(AND(Dados!A8&lt;&gt;"", Dados!A10&lt;&gt;""), Dados!A8,"")</f>
         <v>{{proprietario_2}}</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="99" t="str">
+      <c r="B44" s="101" t="str">
         <f>IF(Dados!A10&lt;&gt;"", "CPF: " &amp; Dados!A10, "")</f>
         <v>CPF: {{num_doc_2}}</v>
       </c>
-      <c r="C44" s="99"/>
-      <c r="D44" s="99"/>
-      <c r="E44" s="99"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="99"/>
-      <c r="J44" s="99"/>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="101"/>
+      <c r="J44" s="101"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B45" s="48"/>
@@ -2490,17 +2485,43 @@
       <c r="E45" s="48"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="99" t="str">
+      <c r="B46" s="101" t="str">
         <f ca="1">Dados!A59</f>
         <v>Sorriso/MT, 18 de maio de 2026</v>
       </c>
-      <c r="C46" s="99"/>
+      <c r="C46" s="101"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J47" s="80"/>
+      <c r="J47" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:H33"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="H6:J6"/>
@@ -2517,32 +2538,6 @@
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:H33"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="74" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3237,7 +3232,7 @@
       </c>
     </row>
     <row r="165" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="64" t="str">
+      <c r="A165" s="62" t="str">
         <f>Dados!A55</f>
         <v>1214579051</v>
       </c>
@@ -3270,7 +3265,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;P/4</oddFooter>
   </headerFooter>
@@ -3313,17 +3308,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="90.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="66" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="67" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="B4" s="70" t="str">
+      <c r="B4" s="68" t="str">
         <f>IF(Dados!A8="", "Eu, ", "Nós, ") &amp; Dados!A4 &amp; ", portador(a) do CPF: " &amp; Dados!A6 &amp;
 IF(Dados!A8="", "", " e " &amp; Dados!A8 &amp; ", portador(a) do CPF: " &amp; Dados!A10) &amp;
 ", " &amp; IF(Dados!A8="", "AUTORIZO ", "AUTORIZAMOS ") &amp; "o profissional " &amp; Dados!A54 &amp; ", " &amp; Dados!A56 &amp;
@@ -3336,65 +3331,65 @@
       <c r="G4" s="6"/>
     </row>
     <row r="5" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="71"/>
+      <c r="B5" s="69"/>
     </row>
     <row r="6" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="70" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="73"/>
+      <c r="B7" s="71"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="71" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="74"/>
+      <c r="B9" s="72"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="71" t="str">
+      <c r="B10" s="69" t="str">
         <f ca="1">Dados!A59</f>
         <v>Sorriso/MT, 18 de maio de 2026</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="71"/>
+      <c r="B11" s="69"/>
     </row>
     <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="71"/>
+      <c r="B12" s="69"/>
     </row>
     <row r="13" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="71"/>
+      <c r="B13" s="69"/>
     </row>
     <row r="14" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="71"/>
+      <c r="B14" s="69"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="75" t="str">
+      <c r="B15" s="73" t="str">
         <f>Dados!A4</f>
         <v>{{proprietario_1}}</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="76" t="str">
+      <c r="B16" s="74" t="str">
         <f>Dados!A6</f>
         <v>{{num_doc_1}}</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="71"/>
+      <c r="B18" s="69"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="81" t="str">
+      <c r="B19" s="78" t="str">
         <f>IF(AND(Dados!A8&lt;&gt;"", Dados!A10&lt;&gt;""), Dados!A8,"")</f>
         <v>{{proprietario_2}}</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="81" t="str">
+      <c r="B20" s="78" t="str">
         <f>IF(Dados!A10&lt;&gt;"", "CPF: " &amp; Dados!A10, "")</f>
         <v>CPF: {{num_doc_2}}</v>
       </c>

--- a/MODELO_Memorial_Planilha_Declaração_R00.xlsx
+++ b/MODELO_Memorial_Planilha_Declaração_R00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\ProTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D79BE1E-285F-4D27-8441-6C91A4FBA7AB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF573A6-6B54-4C3F-90D6-BEB12BAA34BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="5" r:id="rId1"/>
@@ -28,6 +28,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -886,7 +895,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1027,6 +1036,10 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1043,6 +1056,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1097,6 +1114,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1107,36 +1128,81 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1146,69 +1212,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1575,7 +1580,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="55" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1595,7 +1600,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="54" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1615,7 +1620,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="109" t="s">
+      <c r="A10" s="54" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1625,25 +1630,25 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="55" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="66" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="56" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="82" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1651,17 +1656,17 @@
       <c r="A16" s="42"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="66" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="110" t="s">
+      <c r="A18" s="56" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="66" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1676,7 +1681,7 @@
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="56" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1691,7 +1696,7 @@
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="57" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1701,7 +1706,7 @@
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="57" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1711,7 +1716,7 @@
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="57" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1721,7 +1726,7 @@
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="57" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1731,12 +1736,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="57" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="57" t="str">
+      <c r="A34" s="58" t="str">
         <f>"" &amp; Dados!A25 &amp; ", lote " &amp; Dados!A27 &amp; ", quadra " &amp; Dados!A29 &amp; ", LOTEAMENTO "&amp; Dados!A31 &amp;", SORRISO/MT."</f>
         <v>{{confrontacao_frente}}, lote {{lote}}, quadra {{quadra}}, LOTEAMENTO {{loteamento}}, SORRISO/MT.</v>
       </c>
@@ -1749,7 +1754,7 @@
       <c r="B35" s="47"/>
     </row>
     <row r="36" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="111" t="s">
+      <c r="A36" s="78" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1762,7 +1767,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="111" t="s">
+      <c r="A38" s="59" t="s">
         <v>145</v>
       </c>
     </row>
@@ -1772,7 +1777,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="112" t="s">
+      <c r="A40" s="60" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1782,7 +1787,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="112" t="s">
+      <c r="A42" s="60" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1792,7 +1797,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="58" t="s">
+      <c r="A44" s="60" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1802,7 +1807,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="61" t="s">
+      <c r="A46" s="63" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1822,7 +1827,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="58" t="s">
+      <c r="A50" s="60" t="s">
         <v>142</v>
       </c>
     </row>
@@ -1842,18 +1847,18 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="59" t="s">
+      <c r="A54" s="61" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="63" t="str">
+      <c r="A55" s="65" t="str">
         <f>IF(A54="LEANDRO DE SOUZA PEREIRA", "1214579051", IF(A54="PAULO MIGUEL GOULART DAL ZOT", "1222999722", "NOME NÃO ENCONTRADO"))</f>
         <v>1214579051</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="59" t="s">
+      <c r="A56" s="61" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1863,11 +1868,11 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="60" t="str">
+      <c r="A59" s="62" t="str">
         <f ca="1">"Sorriso/MT, " &amp; TEXT(TODAY(),"dd ""de"" mmmm ""de"" aaaa")</f>
         <v>Sorriso/MT, 18 de maio de 2026</v>
       </c>
-      <c r="D59" s="75"/>
+      <c r="D59" s="77"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -1875,7 +1880,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="59" t="s">
+      <c r="A62" s="61" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1934,18 +1939,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -2009,19 +2014,19 @@
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="82"/>
+      <c r="E6" s="85"/>
       <c r="F6" s="6"/>
       <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="H6" s="81" t="s">
+      <c r="H6" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="83"/>
-      <c r="J6" s="82"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="85"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
@@ -2033,39 +2038,39 @@
         <f>Dados!A27</f>
         <v>{{lote}}</v>
       </c>
-      <c r="D7" s="84" t="str">
+      <c r="D7" s="95" t="str">
         <f>Dados!A29</f>
         <v>{{quadra}}</v>
       </c>
-      <c r="E7" s="86"/>
+      <c r="E7" s="90"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="90" t="str">
+      <c r="H7" s="108" t="str">
         <f>Dados!A31</f>
         <v>{{loteamento}}</v>
       </c>
-      <c r="I7" s="91"/>
-      <c r="J7" s="92"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="82"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="85"/>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
         <v>4</v>
       </c>
-      <c r="H9" s="81" t="s">
+      <c r="H9" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="83"/>
-      <c r="J9" s="82"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="85"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
@@ -2078,12 +2083,12 @@
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="87" t="str">
+      <c r="H10" s="107" t="str">
         <f>Dados!A22</f>
         <v>{{area}}</v>
       </c>
-      <c r="I10" s="88"/>
-      <c r="J10" s="89"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
@@ -2095,12 +2100,12 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="83" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="82"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="85"/>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
         <v>6</v>
@@ -2113,10 +2118,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
       <c r="F13" s="6"/>
       <c r="G13" s="4"/>
       <c r="H13" s="11"/>
@@ -2125,21 +2130,21 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="93" t="str">
+      <c r="B14" s="100" t="str">
         <f>IF(AND(Dados!A16&lt;&gt;"", Dados!B16&lt;&gt;""), Dados!A16,"")</f>
         <v/>
       </c>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="76" t="str">
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="79" t="str">
         <f>IF(Dados!A16&lt;&gt;"",Dados!A16,"")</f>
         <v/>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="86"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="90"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
@@ -2151,35 +2156,35 @@
       <c r="A16" s="4">
         <v>7</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="82"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="85"/>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>8</v>
       </c>
-      <c r="H16" s="81" t="s">
+      <c r="H16" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="83"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="85"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="86"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="90"/>
       <c r="F17" s="8"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="87">
+      <c r="H17" s="107">
         <v>0</v>
       </c>
-      <c r="I17" s="88"/>
-      <c r="J17" s="89"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="93"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -2192,12 +2197,12 @@
       <c r="D19" s="5">
         <v>10</v>
       </c>
-      <c r="E19" s="81" t="s">
+      <c r="E19" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="82"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="85"/>
       <c r="I19" s="12">
         <v>11</v>
       </c>
@@ -2207,19 +2212,19 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="107" t="str">
+      <c r="B20" s="89" t="str">
         <f>E10</f>
         <v>{{area_construida_total}}</v>
       </c>
-      <c r="C20" s="86"/>
+      <c r="C20" s="90"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="108">
+      <c r="E20" s="91">
         <f>B17+H17</f>
         <v>0</v>
       </c>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="89"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="93"/>
       <c r="I20" s="15"/>
       <c r="J20" s="46" t="str">
         <f>B20</f>
@@ -2230,51 +2235,51 @@
       <c r="A22" s="4">
         <v>12</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="82"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="85"/>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>13</v>
       </c>
-      <c r="H22" s="81" t="s">
+      <c r="H22" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="83"/>
-      <c r="J22" s="82"/>
-      <c r="L22" s="77"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="85"/>
+      <c r="L22" s="80"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="107" t="str">
+      <c r="B23" s="89" t="str">
         <f>B20</f>
         <v>{{area_construida_total}}</v>
       </c>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="86"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="90"/>
       <c r="F23" s="8"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="84" t="str">
+      <c r="H23" s="95" t="str">
         <f>Dados!A44</f>
         <v>{{numero_vagas}}</v>
       </c>
-      <c r="I23" s="85"/>
-      <c r="J23" s="86"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>14</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="82"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="85"/>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
         <v>15</v>
@@ -2291,13 +2296,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="95" t="e">
+      <c r="B26" s="86" t="e">
         <f>1-((B23)/H10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="97"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="88"/>
       <c r="F26" s="8"/>
       <c r="G26" s="7"/>
       <c r="H26" s="16" t="str">
@@ -2314,54 +2319,54 @@
       <c r="A28" s="4">
         <v>17</v>
       </c>
-      <c r="B28" s="81" t="s">
+      <c r="B28" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="82"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="85"/>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>18</v>
       </c>
-      <c r="H28" s="81" t="s">
+      <c r="H28" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="I28" s="83"/>
-      <c r="J28" s="82"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="85"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="95" t="e">
+      <c r="B29" s="86" t="e">
         <f>B23/H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="97"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="88"/>
       <c r="F29" s="8"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="98" t="e">
+      <c r="H29" s="96" t="e">
         <f>B20/H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I29" s="99"/>
-      <c r="J29" s="100"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="98"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>19</v>
       </c>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="65" t="str">
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="67" t="str">
         <f>IF(Dados!A14=J31, "X", "")</f>
         <v>X</v>
       </c>
@@ -2370,18 +2375,18 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="102"/>
-      <c r="B32" s="103" t="str">
+      <c r="A32" s="101"/>
+      <c r="B32" s="102" t="str">
         <f>Dados!A12</f>
         <v>RESIDENCIAL E COMERCIAL</v>
       </c>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="65" t="str">
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="67" t="str">
         <f>IF(Dados!A14=J32, "X", "")</f>
         <v/>
       </c>
@@ -2390,15 +2395,15 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="102"/>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="65" t="str">
+      <c r="A33" s="101"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="67" t="str">
         <f>IF(Dados!A14=J33, "X", "")</f>
         <v/>
       </c>
@@ -2413,70 +2418,70 @@
       <c r="H35" t="s">
         <v>27</v>
       </c>
-      <c r="J35" s="77"/>
+      <c r="J35" s="80"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O37" s="22"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="104" t="str">
+      <c r="B39" s="103" t="str">
         <f>C3</f>
         <v>{{proprietario_1}}</v>
       </c>
-      <c r="C39" s="104"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="H39" s="104" t="str">
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="H39" s="103" t="str">
         <f>Dados!A54</f>
         <v>LEANDRO DE SOUZA PEREIRA</v>
       </c>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
+      <c r="I39" s="103"/>
+      <c r="J39" s="103"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="105" t="str">
+      <c r="B40" s="104" t="str">
         <f>B4</f>
         <v>{{num_doc_1}}</v>
       </c>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="H40" s="106" t="str">
+      <c r="C40" s="104"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="H40" s="105" t="str">
         <f>Dados!A55</f>
         <v>1214579051</v>
       </c>
-      <c r="I40" s="106"/>
-      <c r="J40" s="106"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="105"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="101"/>
-      <c r="C42" s="101"/>
-      <c r="D42" s="101"/>
-      <c r="E42" s="101"/>
+      <c r="B42" s="99"/>
+      <c r="C42" s="99"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="99"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="101" t="str">
+      <c r="B43" s="99" t="str">
         <f>IF(AND(Dados!A8&lt;&gt;"", Dados!A10&lt;&gt;""), Dados!A8,"")</f>
         <v>{{proprietario_2}}</v>
       </c>
-      <c r="C43" s="101"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="101"/>
-      <c r="H43" s="101"/>
-      <c r="I43" s="101"/>
-      <c r="J43" s="101"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="101" t="str">
+      <c r="B44" s="99" t="str">
         <f>IF(Dados!A10&lt;&gt;"", "CPF: " &amp; Dados!A10, "")</f>
         <v>CPF: {{num_doc_2}}</v>
       </c>
-      <c r="C44" s="101"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="101"/>
-      <c r="H44" s="101"/>
-      <c r="I44" s="101"/>
-      <c r="J44" s="101"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B45" s="48"/>
@@ -2485,43 +2490,17 @@
       <c r="E45" s="48"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="101" t="str">
+      <c r="B46" s="99" t="str">
         <f ca="1">Dados!A59</f>
         <v>Sorriso/MT, 18 de maio de 2026</v>
       </c>
-      <c r="C46" s="101"/>
+      <c r="C46" s="99"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="J47" s="77"/>
+      <c r="J47" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:H33"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B42:E42"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="H6:J6"/>
@@ -2538,6 +2517,32 @@
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:H33"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="74" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3232,7 +3237,7 @@
       </c>
     </row>
     <row r="165" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="62" t="str">
+      <c r="A165" s="64" t="str">
         <f>Dados!A55</f>
         <v>1214579051</v>
       </c>
@@ -3265,7 +3270,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;P/4</oddFooter>
   </headerFooter>
@@ -3308,17 +3313,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="90.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="69" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="B4" s="68" t="str">
+      <c r="B4" s="70" t="str">
         <f>IF(Dados!A8="", "Eu, ", "Nós, ") &amp; Dados!A4 &amp; ", portador(a) do CPF: " &amp; Dados!A6 &amp;
 IF(Dados!A8="", "", " e " &amp; Dados!A8 &amp; ", portador(a) do CPF: " &amp; Dados!A10) &amp;
 ", " &amp; IF(Dados!A8="", "AUTORIZO ", "AUTORIZAMOS ") &amp; "o profissional " &amp; Dados!A54 &amp; ", " &amp; Dados!A56 &amp;
@@ -3331,65 +3336,65 @@
       <c r="G4" s="6"/>
     </row>
     <row r="5" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="69"/>
+      <c r="B5" s="71"/>
     </row>
     <row r="6" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="72" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="71"/>
+      <c r="B7" s="73"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="73" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="72"/>
+      <c r="B9" s="74"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="69" t="str">
+      <c r="B10" s="71" t="str">
         <f ca="1">Dados!A59</f>
         <v>Sorriso/MT, 18 de maio de 2026</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="69"/>
+      <c r="B11" s="71"/>
     </row>
     <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="69"/>
+      <c r="B12" s="71"/>
     </row>
     <row r="13" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="69"/>
+      <c r="B13" s="71"/>
     </row>
     <row r="14" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="69"/>
+      <c r="B14" s="71"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="73" t="str">
+      <c r="B15" s="75" t="str">
         <f>Dados!A4</f>
         <v>{{proprietario_1}}</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="str">
+      <c r="B16" s="76" t="str">
         <f>Dados!A6</f>
         <v>{{num_doc_1}}</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="69"/>
+      <c r="B18" s="71"/>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="78" t="str">
+      <c r="B19" s="81" t="str">
         <f>IF(AND(Dados!A8&lt;&gt;"", Dados!A10&lt;&gt;""), Dados!A8,"")</f>
         <v>{{proprietario_2}}</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="78" t="str">
+      <c r="B20" s="81" t="str">
         <f>IF(Dados!A10&lt;&gt;"", "CPF: " &amp; Dados!A10, "")</f>
         <v>CPF: {{num_doc_2}}</v>
       </c>

--- a/MODELO_Memorial_Planilha_Declaração_R00.xlsx
+++ b/MODELO_Memorial_Planilha_Declaração_R00.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\ProTool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\ProTool\ProTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF573A6-6B54-4C3F-90D6-BEB12BAA34BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA22C8E-C95A-4A2E-8D63-1815EA6E9FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
   </bookViews>
@@ -556,21 +556,12 @@
     <t>LEANDRO DE SOUZA PEREIRA</t>
   </si>
   <si>
-    <t>RESIDENCIAL E COMERCIAL</t>
-  </si>
-  <si>
-    <t>ZC2 / ZCT3</t>
-  </si>
-  <si>
     <t>Nº ALVARÁ</t>
   </si>
   <si>
     <t>Estou igualmente ciente de que todas as taxas decorrentes deste processo serão emitidas em nome(s) aqui representado(s), enquanto proprietário(s) do imóvel, e assumo total responsabilidade pelo seu pagamento.</t>
   </si>
   <si>
-    <t>CONSTRUÇÃO DE UMA EDIFICAÇÃO RESIDENCIAL UNIFAMILIAR</t>
-  </si>
-  <si>
     <t>{{proprietario_1}}</t>
   </si>
   <si>
@@ -629,6 +620,15 @@
   </si>
   <si>
     <t>{{cep}}</t>
+  </si>
+  <si>
+    <t>{{zona_zoneamento}}</t>
+  </si>
+  <si>
+    <t>{{finalidade_obra}}</t>
+  </si>
+  <si>
+    <t>CONSTRUÇÃO DE UMA EDIFICAÇÃO {{finalidade_obra}}</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="53" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1601,7 +1601,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1621,7 +1621,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="54" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1630,8 +1630,8 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
-        <v>121</v>
+      <c r="A12" s="20" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1649,7 +1649,7 @@
         <v>95</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -1662,7 +1662,7 @@
     </row>
     <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
     </row>
     <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="56" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -1697,7 +1697,7 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="57" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="57" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="57" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -1737,7 +1737,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="57" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="36" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="78" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1768,7 +1768,7 @@
     </row>
     <row r="38" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,7 @@
     </row>
     <row r="40" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="60" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1788,7 +1788,7 @@
     </row>
     <row r="42" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="60" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
     </row>
     <row r="44" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="60" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1808,7 +1808,7 @@
     </row>
     <row r="46" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="63" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1818,17 +1818,17 @@
     </row>
     <row r="48" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="43" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="60" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1838,7 +1838,7 @@
     </row>
     <row r="52" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1870,7 +1870,7 @@
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="62" t="str">
         <f ca="1">"Sorriso/MT, " &amp; TEXT(TODAY(),"dd ""de"" mmmm ""de"" aaaa")</f>
-        <v>Sorriso/MT, 18 de maio de 2026</v>
+        <v>Sorriso/MT, 21 de maio de 2026</v>
       </c>
       <c r="D59" s="77"/>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A46" xr:uid="{2A4651C4-232B-45D8-9BA7-08F52FD8DBC9}">
       <formula1>"meia água embutido na platibanda, duas águas embutidas na platibanda, telhado aparente meia água, telhado aparente duas águas, telhado aparente quatro águas,"</formula1>
     </dataValidation>
@@ -1904,9 +1904,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A14" xr:uid="{BA5BED0E-9CE4-4B91-8860-B4EFB52B9F36}">
       <formula1>"Alvenaria, Madeira, Pré-moldado"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A12" xr:uid="{C0E477A5-44CB-43E4-8A71-57B5B1946DB1}">
-      <formula1>"RESIDENCIAL UNIFAMILIAR, RESIDENCIAL MULTIFAMILIAR, COMERCIAL, RESIDENCIAL E COMERCIAL"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -2032,7 +2029,7 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="str">
         <f>Dados!A33</f>
-        <v>ZC2 / ZCT3</v>
+        <v>{{zona_zoneamento}}</v>
       </c>
       <c r="C7" s="7" t="str">
         <f>Dados!A27</f>
@@ -2378,7 +2375,7 @@
       <c r="A32" s="101"/>
       <c r="B32" s="102" t="str">
         <f>Dados!A12</f>
-        <v>RESIDENCIAL E COMERCIAL</v>
+        <v>{{finalidade_obra}}</v>
       </c>
       <c r="C32" s="102"/>
       <c r="D32" s="102"/>
@@ -2492,7 +2489,7 @@
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B46" s="99" t="str">
         <f ca="1">Dados!A59</f>
-        <v>Sorriso/MT, 18 de maio de 2026</v>
+        <v>Sorriso/MT, 21 de maio de 2026</v>
       </c>
       <c r="C46" s="99"/>
     </row>
@@ -2645,7 +2642,7 @@
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="str">
         <f>Dados!A12</f>
-        <v>RESIDENCIAL E COMERCIAL</v>
+        <v>{{finalidade_obra}}</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3250,7 +3247,7 @@
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="str">
         <f ca="1">Dados!A59</f>
-        <v>Sorriso/MT, 18 de maio de 2026</v>
+        <v>Sorriso/MT, 21 de maio de 2026</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
@@ -3340,7 +3337,7 @@
     </row>
     <row r="6" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="B6" s="72" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -3357,7 +3354,7 @@
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="71" t="str">
         <f ca="1">Dados!A59</f>
-        <v>Sorriso/MT, 18 de maio de 2026</v>
+        <v>Sorriso/MT, 21 de maio de 2026</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/MODELO_Memorial_Planilha_Declaração_R00.xlsx
+++ b/MODELO_Memorial_Planilha_Declaração_R00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\ProTool\ProTool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA22C8E-C95A-4A2E-8D63-1815EA6E9FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52351545-F6AB-42F8-AEBA-E1D89D63D04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{1E7CDECE-C019-4B9C-999A-C8660DDB49AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="5" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="145">
   <si>
     <t>FINALIDADE DA OBRA:</t>
   </si>
@@ -626,9 +626,6 @@
   </si>
   <si>
     <t>{{finalidade_obra}}</t>
-  </si>
-  <si>
-    <t>CONSTRUÇÃO DE UMA EDIFICAÇÃO {{finalidade_obra}}</t>
   </si>
 </sst>
 </file>
@@ -1128,14 +1125,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1146,74 +1179,38 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1581,7 +1578,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1870,7 +1867,7 @@
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="62" t="str">
         <f ca="1">"Sorriso/MT, " &amp; TEXT(TODAY(),"dd ""de"" mmmm ""de"" aaaa")</f>
-        <v>Sorriso/MT, 21 de maio de 2026</v>
+        <v>Sorriso/MT, 28 de maio de 2026</v>
       </c>
       <c r="D59" s="77"/>
     </row>
@@ -1936,18 +1933,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -2011,7 +2008,7 @@
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="84" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="85"/>
@@ -2019,10 +2016,10 @@
       <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="84"/>
+      <c r="I6" s="86"/>
       <c r="J6" s="85"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2035,38 +2032,38 @@
         <f>Dados!A27</f>
         <v>{{lote}}</v>
       </c>
-      <c r="D7" s="95" t="str">
+      <c r="D7" s="87" t="str">
         <f>Dados!A29</f>
         <v>{{quadra}}</v>
       </c>
-      <c r="E7" s="90"/>
+      <c r="E7" s="89"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="108" t="str">
+      <c r="H7" s="93" t="str">
         <f>Dados!A31</f>
         <v>{{loteamento}}</v>
       </c>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="85"/>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
         <v>4</v>
       </c>
-      <c r="H9" s="83" t="s">
+      <c r="H9" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="84"/>
+      <c r="I9" s="86"/>
       <c r="J9" s="85"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2080,12 +2077,12 @@
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="107" t="str">
+      <c r="H10" s="90" t="str">
         <f>Dados!A22</f>
         <v>{{area}}</v>
       </c>
-      <c r="I10" s="92"/>
-      <c r="J10" s="93"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
@@ -2097,11 +2094,11 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
       <c r="E12" s="85"/>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
@@ -2115,10 +2112,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
       <c r="F13" s="6"/>
       <c r="G13" s="4"/>
       <c r="H13" s="11"/>
@@ -2127,21 +2124,21 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="100" t="str">
-        <f>IF(AND(Dados!A16&lt;&gt;"", Dados!B16&lt;&gt;""), Dados!A16,"")</f>
+      <c r="B14" s="96" t="str">
+        <f>IF(AND(Dados!A16&lt;&gt;"", Dados!B16&lt;&gt;""), Dados!B16,"")</f>
         <v/>
       </c>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
       <c r="E14" s="79" t="str">
         <f>IF(Dados!A16&lt;&gt;"",Dados!A16,"")</f>
         <v/>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="90"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="89"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
@@ -2153,35 +2150,35 @@
       <c r="A16" s="4">
         <v>7</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="85"/>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>8</v>
       </c>
-      <c r="H16" s="83" t="s">
+      <c r="H16" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="84"/>
+      <c r="I16" s="86"/>
       <c r="J16" s="85"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="90"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="89"/>
       <c r="F17" s="8"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="107">
+      <c r="H17" s="90">
         <v>0</v>
       </c>
-      <c r="I17" s="92"/>
-      <c r="J17" s="93"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -2194,11 +2191,11 @@
       <c r="D19" s="5">
         <v>10</v>
       </c>
-      <c r="E19" s="83" t="s">
+      <c r="E19" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
       <c r="H19" s="85"/>
       <c r="I19" s="12">
         <v>11</v>
@@ -2209,19 +2206,19 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="89" t="str">
-        <f>E10</f>
+      <c r="B20" s="110" t="str">
+        <f>IF(E14&lt;&gt;"", E10+E14, E10)</f>
         <v>{{area_construida_total}}</v>
       </c>
-      <c r="C20" s="90"/>
+      <c r="C20" s="89"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="91">
+      <c r="E20" s="111">
         <f>B17+H17</f>
         <v>0</v>
       </c>
-      <c r="F20" s="92"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="93"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="92"/>
       <c r="I20" s="15"/>
       <c r="J20" s="46" t="str">
         <f>B20</f>
@@ -2232,50 +2229,50 @@
       <c r="A22" s="4">
         <v>12</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
       <c r="E22" s="85"/>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>13</v>
       </c>
-      <c r="H22" s="83" t="s">
+      <c r="H22" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="84"/>
+      <c r="I22" s="86"/>
       <c r="J22" s="85"/>
       <c r="L22" s="80"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="89" t="str">
+      <c r="B23" s="110" t="str">
         <f>B20</f>
         <v>{{area_construida_total}}</v>
       </c>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="90"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="8"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="95" t="str">
+      <c r="H23" s="87" t="str">
         <f>Dados!A44</f>
         <v>{{numero_vagas}}</v>
       </c>
-      <c r="I23" s="94"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>14</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
       <c r="E25" s="85"/>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
@@ -2293,13 +2290,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
-      <c r="B26" s="86" t="e">
+      <c r="B26" s="98" t="e">
         <f>1-((B23)/H10)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="88"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="100"/>
       <c r="F26" s="8"/>
       <c r="G26" s="7"/>
       <c r="H26" s="16" t="str">
@@ -2316,53 +2313,53 @@
       <c r="A28" s="4">
         <v>17</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="84"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
       <c r="E28" s="85"/>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>18</v>
       </c>
-      <c r="H28" s="83" t="s">
+      <c r="H28" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="I28" s="84"/>
+      <c r="I28" s="86"/>
       <c r="J28" s="85"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="86" t="e">
+      <c r="B29" s="98" t="e">
         <f>B23/H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="88"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="100"/>
       <c r="F29" s="8"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="96" t="e">
+      <c r="H29" s="101" t="e">
         <f>B20/H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I29" s="97"/>
-      <c r="J29" s="98"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="103"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>19</v>
       </c>
-      <c r="B31" s="100" t="s">
+      <c r="B31" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
       <c r="I31" s="67" t="str">
         <f>IF(Dados!A14=J31, "X", "")</f>
         <v>X</v>
@@ -2372,17 +2369,17 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="101"/>
-      <c r="B32" s="102" t="str">
+      <c r="A32" s="105"/>
+      <c r="B32" s="106" t="str">
         <f>Dados!A12</f>
         <v>{{finalidade_obra}}</v>
       </c>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="102"/>
+      <c r="C32" s="106"/>
+      <c r="D32" s="106"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="106"/>
       <c r="I32" s="67" t="str">
         <f>IF(Dados!A14=J32, "X", "")</f>
         <v/>
@@ -2392,14 +2389,14 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="101"/>
-      <c r="B33" s="102"/>
-      <c r="C33" s="102"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="102"/>
-      <c r="F33" s="102"/>
-      <c r="G33" s="102"/>
-      <c r="H33" s="102"/>
+      <c r="A33" s="105"/>
+      <c r="B33" s="106"/>
+      <c r="C33" s="106"/>
+      <c r="D33" s="106"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="106"/>
       <c r="I33" s="67" t="str">
         <f>IF(Dados!A14=J33, "X", "")</f>
         <v/>
@@ -2421,64 +2418,64 @@
       <c r="O37" s="22"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="103" t="str">
+      <c r="B39" s="107" t="str">
         <f>C3</f>
         <v>{{proprietario_1}}</v>
       </c>
-      <c r="C39" s="103"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="H39" s="103" t="str">
+      <c r="C39" s="107"/>
+      <c r="D39" s="107"/>
+      <c r="E39" s="107"/>
+      <c r="H39" s="107" t="str">
         <f>Dados!A54</f>
         <v>LEANDRO DE SOUZA PEREIRA</v>
       </c>
-      <c r="I39" s="103"/>
-      <c r="J39" s="103"/>
+      <c r="I39" s="107"/>
+      <c r="J39" s="107"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="104" t="str">
+      <c r="B40" s="108" t="str">
         <f>B4</f>
         <v>{{num_doc_1}}</v>
       </c>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="H40" s="105" t="str">
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="H40" s="109" t="str">
         <f>Dados!A55</f>
         <v>1214579051</v>
       </c>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
+      <c r="I40" s="109"/>
+      <c r="J40" s="109"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="99"/>
-      <c r="C42" s="99"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="99"/>
+      <c r="B42" s="104"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="99" t="str">
+      <c r="B43" s="104" t="str">
         <f>IF(AND(Dados!A8&lt;&gt;"", Dados!A10&lt;&gt;""), Dados!A8,"")</f>
         <v>{{proprietario_2}}</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="99" t="str">
+      <c r="B44" s="104" t="str">
         <f>IF(Dados!A10&lt;&gt;"", "CPF: " &amp; Dados!A10, "")</f>
         <v>CPF: {{num_doc_2}}</v>
       </c>
-      <c r="C44" s="99"/>
-      <c r="D44" s="99"/>
-      <c r="E44" s="99"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="99"/>
-      <c r="J44" s="99"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B45" s="48"/>
@@ -2487,17 +2484,43 @@
       <c r="E45" s="48"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="99" t="str">
+      <c r="B46" s="104" t="str">
         <f ca="1">Dados!A59</f>
-        <v>Sorriso/MT, 21 de maio de 2026</v>
-      </c>
-      <c r="C46" s="99"/>
+        <v>Sorriso/MT, 28 de maio de 2026</v>
+      </c>
+      <c r="C46" s="104"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J47" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:H33"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="H6:J6"/>
@@ -2514,32 +2537,6 @@
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:H33"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="74" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3247,7 +3244,7 @@
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="str">
         <f ca="1">Dados!A59</f>
-        <v>Sorriso/MT, 21 de maio de 2026</v>
+        <v>Sorriso/MT, 28 de maio de 2026</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
@@ -3267,7 +3264,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;P/4</oddFooter>
   </headerFooter>
@@ -3354,7 +3351,7 @@
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="71" t="str">
         <f ca="1">Dados!A59</f>
-        <v>Sorriso/MT, 21 de maio de 2026</v>
+        <v>Sorriso/MT, 28 de maio de 2026</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
